--- a/artfynd/A 13256-2026 artfynd.xlsx
+++ b/artfynd/A 13256-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99845159</v>
+        <v>99845144</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629402.6233121769</v>
+        <v>629403</v>
       </c>
       <c r="R2" t="n">
-        <v>6517817.687882804</v>
+        <v>6517817</v>
       </c>
       <c r="S2" t="n">
         <v>21</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,16 +797,11 @@
         <v>99845140</v>
       </c>
       <c r="B3" t="n">
-        <v>55511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -851,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629402.6233121769</v>
+        <v>629403</v>
       </c>
       <c r="R3" t="n">
-        <v>6517817.687882804</v>
+        <v>6517817</v>
       </c>
       <c r="S3" t="n">
         <v>21</v>
@@ -920,6 +910,363 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99845146</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyköping, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629403</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6517817</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tystberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kalle Brinell, Samuel Wivstad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99845158</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyköping, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629403</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6517817</v>
+      </c>
+      <c r="S5" t="n">
+        <v>21</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tystberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kalle Brinell, Samuel Wivstad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99845159</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyköping, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629403</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6517817</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tystberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kalle Brinell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kalle Brinell, Samuel Wivstad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13256-2026 artfynd.xlsx
+++ b/artfynd/A 13256-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99845144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99845140</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99845146</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99845158</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,8 +1292,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99845159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>